--- a/data/trans_orig/KIDM_A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30340</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41073</t>
+          <t>41119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94141</t>
+          <t>94184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65005</t>
+          <t>65146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19248</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>39591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45787</t>
+          <t>46179</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97852</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66198</t>
+          <t>66670</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64448</t>
+          <t>64323</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133090</t>
+          <t>133181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>271214</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>280393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>291820</t>
+          <t>290633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>299475</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>566540</t>
+          <t>567436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>578173</t>
+          <t>578572</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50177</t>
+          <t>49814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41569</t>
+          <t>41468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46261</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>94237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99537</t>
+          <t>99539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27621</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33325</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>65019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71614</t>
+          <t>71475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41557</t>
+          <t>41538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>43838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87424</t>
+          <t>88165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93408</t>
+          <t>93420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67180</t>
+          <t>67699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72413</t>
+          <t>72418</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70409</t>
+          <t>70405</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75054</t>
+          <t>75049</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140058</t>
+          <t>140169</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147145</t>
+          <t>147209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>276813</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>287302</t>
+          <t>286730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>294876</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>305092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>575732</t>
+          <t>576074</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>590640</t>
+          <t>591012</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>40235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>46951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>48613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>50748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>102852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26303</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28763</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59046</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56309</t>
+          <t>56081</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>110382</t>
+          <t>111533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>73967</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>143567</t>
+          <t>143135</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>314949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>321914</t>
+          <t>322012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>314754</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>323553</t>
+          <t>323568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>633479</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>643740</t>
+          <t>644278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>55914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112265</t>
+          <t>113117</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119398</t>
+          <t>119327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>41348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>965</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38295</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12835,7 +12835,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>43308</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70436</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>75189</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>140221</t>
+          <t>139325</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>204751</t>
+          <t>204124</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>210620</t>
+          <t>210561</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>264586</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>272001</t>
+          <t>271983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>472475</t>
+          <t>471831</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>481647</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
